--- a/Cardiologie/Excel/cardio_11.xlsx
+++ b/Cardiologie/Excel/cardio_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0D758B-2B26-4D5F-8549-7DCEE1835E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A3D4BB-D4D5-4AA4-9472-604BC39EA9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,16 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="131">
-  <si>
-    <t>numero</t>
-  </si>
-  <si>
-    <t>proposition</t>
-  </si>
-  <si>
-    <t>reponse</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
   <si>
     <t>La vascularisation de l'intestin grêle et du côlon est assurée uniquement par le tronc coeliaque.</t>
   </si>
@@ -409,26 +400,33 @@
     <t>La tomodensitométrie avec injection de produit de contraste permet de faire le diagnostic différentiel de la colite ischémique et d’observer les vaisseaux mésentériques.</t>
   </si>
   <si>
-    <t>Faux</t>
-  </si>
-  <si>
-    <t>Vrai</t>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Proposition</t>
+  </si>
+  <si>
+    <t>Reponse</t>
+  </si>
+  <si>
+    <t>Justification</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>image</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -444,27 +442,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -473,11 +456,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,1410 +766,1422 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="186.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="186.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
+      <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="B10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="B15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C18" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="B20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C20" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="B21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>22</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
+      <c r="B23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
         <v>24</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="B25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C25" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="B27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
         <v>27</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="C30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
         <v>30</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="B31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>31</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="B32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C32" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
         <v>32</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="B33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="C33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
+      <c r="B34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="C34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
         <v>34</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
+      <c r="B35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="C35" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
+      <c r="B36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C36" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>36</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
+      <c r="B37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C37" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
         <v>37</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
+      <c r="B38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C38" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
         <v>38</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
+      <c r="B39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C39" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
         <v>39</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
+      <c r="B40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="C40" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C41" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
         <v>41</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
+      <c r="B42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C42" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
         <v>42</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="B43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C43" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
+      <c r="B44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C44" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
         <v>44</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
+      <c r="B45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
+      <c r="B46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C46" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
+      <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C47" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
         <v>47</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
+      <c r="B48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C48" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
         <v>48</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" s="2">
+      <c r="B49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C49" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
         <v>49</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
+      <c r="B50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C50" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>50</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+      <c r="B51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C51" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>51</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" s="2">
+      <c r="B52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C52" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>52</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="B53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
         <v>53</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" s="2">
+      <c r="B54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C54" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
         <v>54</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="2">
+      <c r="B55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C55" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
         <v>55</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
+      <c r="B56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C56" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
+      <c r="B57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C57" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
         <v>57</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="2">
+      <c r="B58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="C58" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
         <v>58</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="2">
+      <c r="B59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C59" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
         <v>59</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="2">
+      <c r="B60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C60" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
         <v>60</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="2">
+      <c r="B61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C61" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
         <v>61</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="2">
+      <c r="B62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C62" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
         <v>62</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+      <c r="B63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="C63" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
         <v>63</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="B64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C64" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="B65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="C65" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
         <v>65</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="2">
+      <c r="B66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="C66" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
         <v>66</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" s="2">
+      <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="C67" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
         <v>67</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" s="2">
+      <c r="B68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="C68" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
         <v>68</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
+      <c r="B69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="C69" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
         <v>69</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
+      <c r="B70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="C70" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
         <v>70</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
+      <c r="B71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="C71" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
         <v>71</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
+      <c r="B72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="C72" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
         <v>72</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
+      <c r="B73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="C73" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
         <v>73</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
+      <c r="B74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="C74" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
         <v>74</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
+      <c r="B75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="C75" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
         <v>75</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
+      <c r="B76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="C76" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
         <v>76</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
+      <c r="B77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="C77" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
         <v>77</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
+      <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="C78" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
         <v>78</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
+      <c r="B79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="C79" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
         <v>79</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
+      <c r="B80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C80" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
         <v>80</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
+      <c r="B81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="C81" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
         <v>81</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
+      <c r="B82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="C82" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
         <v>82</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
+      <c r="B83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="C83" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
         <v>83</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
+      <c r="B84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C84" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>84</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
+      <c r="B85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="C85" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
         <v>85</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
+      <c r="B86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="C86" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
         <v>86</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
+      <c r="B87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="C87" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
         <v>87</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
+      <c r="B88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="C88" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
         <v>88</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
+      <c r="B89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="C89" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
         <v>89</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
+      <c r="B90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="C90" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
         <v>90</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
+      <c r="B91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="C91" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
         <v>91</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
+      <c r="B92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="C92" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
         <v>92</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+      <c r="B93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="C93" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
         <v>93</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
+      <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="C94" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
         <v>94</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
+      <c r="B95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="C95" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
         <v>95</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
+      <c r="B96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="C96" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
         <v>96</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+      <c r="B97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C97" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
         <v>97</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
+      <c r="B98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C98" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
         <v>98</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
+      <c r="B99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="C99" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
         <v>99</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="2">
+      <c r="B100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="C100" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
         <v>100</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="2">
+      <c r="B101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="C101" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
         <v>101</v>
       </c>
-      <c r="C100" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="C102" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
         <v>102</v>
       </c>
-      <c r="C101" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="2">
+      <c r="B103" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="C103" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
         <v>103</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="2">
+      <c r="B104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="C104" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
         <v>104</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="2">
+      <c r="B105" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="C105" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
         <v>105</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="2">
+      <c r="B106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="C106" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
         <v>106</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="2">
+      <c r="B107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="C107" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
         <v>107</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="2">
+      <c r="B108" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C108" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
         <v>108</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="2">
+      <c r="B109" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C109" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
         <v>109</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="2">
+      <c r="B110" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="C110" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>110</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="2">
+      <c r="B111" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="C111" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
         <v>111</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="B112" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="C112" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
         <v>112</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="2">
+      <c r="B113" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="C113" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
         <v>113</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="2">
+      <c r="B114" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C114" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
         <v>114</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="2">
+      <c r="B115" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="C115" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
         <v>115</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="2">
+      <c r="B116" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="C116" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
         <v>116</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="2">
+      <c r="B117" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="C117" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
         <v>117</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="2">
+      <c r="B118" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="C118" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
         <v>118</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+      <c r="B119" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="C119" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
         <v>119</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="2">
+      <c r="B120" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C120" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
         <v>120</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="2">
+      <c r="B121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="C121" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
         <v>121</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="2">
+      <c r="B122" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="C122" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
         <v>122</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
+      <c r="B123" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="C123" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
         <v>123</v>
       </c>
-      <c r="C122" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="2">
+      <c r="B124" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="C124" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
         <v>124</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="2">
+      <c r="B125" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="C125" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
         <v>125</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="2">
+      <c r="B126" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="C126" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
         <v>126</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="2">
+      <c r="B127" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="2">
-        <v>126</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>130</v>
+      <c r="C127" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Cardiologie/Excel/cardio_11.xlsx
+++ b/Cardiologie/Excel/cardio_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Cardiologie\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A3D4BB-D4D5-4AA4-9472-604BC39EA9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FAA380B-FF77-4FFB-8805-AFBE8DB9671C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="260">
   <si>
     <t>La vascularisation de l'intestin grêle et du côlon est assurée uniquement par le tronc coeliaque.</t>
   </si>
@@ -419,6 +419,387 @@
   </si>
   <si>
     <t>image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La vascularisation est assurée par le tronc cœliaque, l’artère mésentérique supérieure et l’artère mésentérique inférieure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette arcade est une anastomose entre l’artère mésentérique supérieure et l’artère mésentérique inférieure </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document précise au contraire que les variations anatomiques sont fréquentes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’athérosclérose est effectivement responsable de plus de 95 % des cas de sténoses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dysplasie fibromusculaire est citée comme une étiologie beaucoup plus rare </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La plupart des sténoses sont asymptomatiques grâce aux nombreuses voies de suppléance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les symptômes surviennent lorsqu'il existe des lésions sur au moins 2 des 3 troncs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’échographie-Doppler est l'examen de dépistage ; l’angiographie est la référence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’angiographie conventionnelle est au contraire considérée comme l’examen de référence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que le traitement endoluminal est de plus en plus utilisé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objectif est effectivement de prévenir la récidive des symptômes et l’ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement médicamenteux des sténoses comprend des antiagrégants, pas forcément d'anticoagulants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs abdominales post-prandiales sont un signe d'ischémie chronique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sitophobie est la crainte de s'alimenter observée dans la forme chronique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un souffle systolique épigastrique est effectivement noté à l’auscultation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces pathologies surviennent le plus souvent chez des patients de plus de 50 ans </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’occlusion veineuse est listée parmi les causes d’ischémie mésentérique aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions cellulaires deviennent irréversibles après 4 h d'ischémie totale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La nécrose de l’épithélium muqueux est effectivement la première atteinte décrite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte mentionne surtout les emboles dans l’artère mésentérique supérieure (AMS) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs sont violentes, crampoïdes puis continues, et situées en péri-ombilical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’examen clinique est au contraire décrit comme souvent pauvre au stade précoce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La biologie montre effectivement une leucocytose précoce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La tomodensitométrie révèle une distension des anses et un épaississement de paroi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’héparinothérapie est préconisée dès que le diagnostic est évoqué </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle peut être primaire (anomalie hémostase) ou secondaire (néoplasie, pancréatite, etc.) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen doit être réalisé sans insufflation pour ne pas déchirer la séreuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical est indiqué en cas de complications comme la péritonite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les calcifications volumineuses sont au contraire listées comme une limite de l’angio-scanner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C’est l’angiographie par résonance magnétique qui a tendance à surestimer les sténoses </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement comprend effectivement des antiagrégants (Aspirine, Clopidogrel) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce symptôme (douleur post-prandiale) caractérise la forme chronique, pas aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La colite ischémique est au contraire une pathologie du sujet âgé </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme qu'elle est la deuxième cause d’hémorragie digestive basse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement principal de la thrombose veineuse mésentérique est l’anticoagulation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle se manifeste par une acidose métabolique (et non alcalose) et une élévation des LDH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La tomodensitométrie montre effectivement un épaississement de la paroi intestinale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’antibiothérapie à large spectre est utilisée sauf pour les formes légères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les thromboses primaires surviennent dans un contexte d’anomalie de l’hémostase </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’administration de catécholamines est un facteur prédisposant cité </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’hypotension et le choc sont des signes cliniques précisés au stade d'occlusion artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le scanner permet effectivement de visualiser le thrombus dans la lumière veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement de référence de la thrombose veineuse est effectivement l’anticoagulation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les nausées, la diarrhée et le méléna sont des présentations cliniques citées </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le contexte de néoplasie est cité parmi les causes de thromboses secondaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le contrôle strict des facteurs de risque athéroscléreux est essentiel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La leucocytose est au contraire décrite comme un signe biologique précoce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen nécessite au contraire une injection de produit de contraste </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'insufflation risque effectivement de déchirer la séreuse en souffrance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les nausées sont citées parmi les symptômes de la présentation clinique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le contexte de pancréatite est cité comme une cause de thrombose veineuse secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle est caractérisée par une vasoconstriction mésentérique disproportionnée </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'angiographie (visualisation de l'embole en cupule concave) qui est l'examen clé pour les emboles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le ballonnement abdominal est effectivement un symptôme cité de la thrombose veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La cirrhose et l'hypertension portale sont des contextes de thrombose veineuse secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La contraception orale est citée comme un facteur associé aux thromboses veineuses secondaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur de la colite ischémique se situe au flanc et à la fosse iliaque gauche (colon descendant/sigmoïde) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe des anastomoses entre l’AMS et l’AMI (arcade de Riolan) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe effectivement de nombreuses anastomoses entre le tronc cœliaque et l’AMS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions siègent effectivement le plus souvent à l’ostium ou sur les premiers centimètres </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dysplasie fibromusculaire et Takayasu sont cités, mais pas la maladie de Takotsubo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La plupart des sténoses sont au contraire asymptomatiques grâce aux suppléances </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des manifestations cliniques s’observent lorsqu’il existe des lésions sur au moins 2 des 3 troncs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'AOMI (athérosclérose périphérique) est fréquemment associée à ces pathologies </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs abdominales post-prandiales surviennent précocement dans les 15-30 minutes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle entraîne au contraire un amaigrissement (sitophobie) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document liste le sujet obèse comme une limite de l’exploration ultrasonore </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise qu’elle a tendance à surestimer les sténoses serrées et présente des artéfacts </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'angiographie conventionnelle nécessite effectivement l'injection de produit de contraste </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’angiographie conventionnelle permet au contraire une étude complète de la vascularisation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’angiographie conventionnelle face et profil est considérée comme l’examen de référence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aspirine et le clopidogrel sont les antiagrégants cités pour la prévention cardiovasculaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seules les lésions symptomatiques doivent faire l’objet d’un traitement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical utilise effectivement le pontage par greffe veineuse ou la réimplantation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement chirurgical par pontage reste la technique de référence </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’occlusion artérielle aiguë représente la majorité des cas (50-70 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document confirme que le volvulus et la hernie étranglée sont des causes extravasculaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les lésions cellulaires deviennent effectivement irréversibles après 4 h d'ischémie totale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie non-occlusive représente environ 20 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'occlusion artérielle aiguë est effectivement responsable de 50-70 % des cas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'occlusion veineuse représente environ 10 % des cas (et non 20 %) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'ischémie atteint d'abord la muqueuse (nécrose de l'épithélium), pas la séreuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les emboles dans l’AMS sont effectivement le plus souvent d’origine cardiaque </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les emboles de microcristaux de cholestérol sont cités comme une cause d'occlusion artérielle </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'atteinte de la musculeuse peut effectivement mener à l'infarctus transmural et à la péritonite </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L’occlusion peut effectivement être causée par une thrombose in situ sur athérosclérose </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'extension à la sous-muqueuse entraîne effectivement œdème et hémorragie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La dissection aortique est citée comme une cause rare d'occlusion artérielle aiguë </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces causes (traumatismes, vasculites, etc.) concernent l'occlusion artérielle, pas veineuse </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'occlusion artérielle aiguë provoque effectivement des douleurs abdominales violentes et continues </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le texte précise que le patient âgé peut être paucisymptomatique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La douleur est péri-ombilicale avec irradiation dans la fosse iliaque DROITE (pas gauche) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen clinique montre une sensibilité et une douleur "disproportionnée" au stade précoce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est l'angiographie (pas la RM) qui montre l'aspect caractéristique en cupule concave </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La résection intestinale est nécessaire uniquement "en cas d’infarctus" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'objectif est effectivement de restaurer la circulation mésentérique et lever l'ischémie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'embolectomie et la revascularisation concernent l'occlusion artérielle (souvent par embole) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois facteurs sont les facteurs prédisposants cités pour l'ischémie non-occlusive </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artériographie conventionnelle montre effectivement une image « d’arbre mort » </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'artériographie conventionnelle est l'examen cité pour le diagnostic de cette forme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement comprend effectivement des vasodilatateurs via le cathéter et une anticoagulation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La splénectomie et le contexte post-opératoire sont des causes de thrombose secondaire </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les douleurs peuvent effectivement évoluer sur plusieurs jours, suggérant un caractère subaigu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elle représente au contraire 50 à 60 % des ischémies digestives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C'est effectivement l'atteinte vasculaire digestive la plus fréquente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il existe effectivement un lien épidémiologique avec l'HTA, le diabète et les maladies CV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'incidence est au contraire décrite comme étant en augmentation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les étiologies se divisent en causes non occlusives et occlusives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes ces causes sont listées dans les étiologies non occlusives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce sont au contraire les médicaments vasoconstricteurs qui sont cités comme cause </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La localisation des douleurs (flanc et fosse iliaque gauche) correspond à ces segments </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'aortographie est citée parmi les causes occlusives de colite ischémique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le cancer et le fécalome sont listés comme des causes d'obstruction colique (occlusives) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La drépanocytose est au contraire citée parmi les maladies hématologiques occlusives </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois pathologies sont listées comme des causes occlusives de colite ischémique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les syndromes myéloprolifératifs et la CIVD sont cités comme causes hématologiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le document décrit au contraire des douleurs abdominales modérées (et non sévères) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ces trois manifestations sont citées dans la présentation clinique ou les complications </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'anticoagulation est indiquée s'il n'y a PAS d'évidence d'ulcère colique hémorragique </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement antiplaquettaire est discuté selon les affections concomitantes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La chirurgie est indiquée en cas de péritonite, d'hémorragie massive ou d'échec médical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le traitement endovasculaire est au contraire une option pour les lésions des troncs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">La sténose secondaire symptomatique est effectivement une indication chirurgicale </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'échec du traitement médical est listé comme une indication au traitement chirurgical </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'antibiothérapie est utilisée sauf pour les formes légères </t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'examen permet effectivement le diagnostic différentiel et l'étude des vaisseaux </t>
+  </si>
+  <si>
+    <t>Page</t>
   </si>
 </sst>
 </file>
@@ -766,7 +1147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
@@ -775,7 +1156,7 @@
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>126</v>
       </c>
@@ -789,16 +1170,19 @@
         <v>129</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -808,8 +1192,14 @@
       <c r="C2" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -819,8 +1209,14 @@
       <c r="C3" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -830,8 +1226,14 @@
       <c r="C4" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -841,8 +1243,14 @@
       <c r="C5" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -852,8 +1260,14 @@
       <c r="C6" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -863,8 +1277,14 @@
       <c r="C7" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -874,8 +1294,14 @@
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -885,8 +1311,14 @@
       <c r="C9" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -896,8 +1328,14 @@
       <c r="C10" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -907,8 +1345,14 @@
       <c r="C11" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -918,8 +1362,14 @@
       <c r="C12" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -929,8 +1379,14 @@
       <c r="C13" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -940,8 +1396,14 @@
       <c r="C14" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -951,8 +1413,14 @@
       <c r="C15" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -962,8 +1430,14 @@
       <c r="C16" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -973,8 +1447,14 @@
       <c r="C17" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -984,8 +1464,14 @@
       <c r="C18" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -995,8 +1481,14 @@
       <c r="C19" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1006,8 +1498,14 @@
       <c r="C20" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1017,8 +1515,14 @@
       <c r="C21" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1028,8 +1532,14 @@
       <c r="C22" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1039,8 +1549,14 @@
       <c r="C23" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1050,8 +1566,14 @@
       <c r="C24" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>155</v>
+      </c>
+      <c r="E24" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1061,8 +1583,14 @@
       <c r="C25" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1072,8 +1600,14 @@
       <c r="C26" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1083,8 +1617,14 @@
       <c r="C27" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1094,8 +1634,14 @@
       <c r="C28" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1105,8 +1651,14 @@
       <c r="C29" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>160</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -1116,8 +1668,14 @@
       <c r="C30" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1127,8 +1685,14 @@
       <c r="C31" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1138,8 +1702,14 @@
       <c r="C32" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1149,8 +1719,14 @@
       <c r="C33" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1160,8 +1736,14 @@
       <c r="C34" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1171,8 +1753,14 @@
       <c r="C35" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>166</v>
+      </c>
+      <c r="E35" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1182,8 +1770,14 @@
       <c r="C36" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1193,8 +1787,14 @@
       <c r="C37" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>168</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1204,8 +1804,14 @@
       <c r="C38" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>169</v>
+      </c>
+      <c r="E38" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1215,8 +1821,14 @@
       <c r="C39" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E39" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1226,8 +1838,14 @@
       <c r="C40" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1237,8 +1855,14 @@
       <c r="C41" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1248,8 +1872,14 @@
       <c r="C42" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1259,8 +1889,14 @@
       <c r="C43" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>174</v>
+      </c>
+      <c r="E43" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1270,8 +1906,14 @@
       <c r="C44" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1281,8 +1923,14 @@
       <c r="C45" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1292,8 +1940,14 @@
       <c r="C46" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>177</v>
+      </c>
+      <c r="E46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1303,8 +1957,14 @@
       <c r="C47" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>178</v>
+      </c>
+      <c r="E47" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1314,8 +1974,14 @@
       <c r="C48" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E48" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1325,8 +1991,14 @@
       <c r="C49" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>180</v>
+      </c>
+      <c r="E49" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1336,8 +2008,14 @@
       <c r="C50" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1347,8 +2025,14 @@
       <c r="C51" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>182</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1358,8 +2042,14 @@
       <c r="C52" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1369,8 +2059,14 @@
       <c r="C53" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1380,8 +2076,14 @@
       <c r="C54" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>185</v>
+      </c>
+      <c r="E54" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1391,8 +2093,14 @@
       <c r="C55" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>186</v>
+      </c>
+      <c r="E55" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1402,8 +2110,14 @@
       <c r="C56" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>187</v>
+      </c>
+      <c r="E56" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1413,8 +2127,14 @@
       <c r="C57" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>188</v>
+      </c>
+      <c r="E57" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1424,8 +2144,14 @@
       <c r="C58" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1435,8 +2161,14 @@
       <c r="C59" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>190</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1446,8 +2178,14 @@
       <c r="C60" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>191</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1457,8 +2195,14 @@
       <c r="C61" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>192</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1468,8 +2212,14 @@
       <c r="C62" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>193</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1479,8 +2229,14 @@
       <c r="C63" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>194</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1490,8 +2246,14 @@
       <c r="C64" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>195</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -1501,8 +2263,14 @@
       <c r="C65" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>196</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -1512,8 +2280,14 @@
       <c r="C66" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>197</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -1523,8 +2297,14 @@
       <c r="C67" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>198</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -1534,8 +2314,14 @@
       <c r="C68" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -1545,8 +2331,14 @@
       <c r="C69" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>200</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -1556,8 +2348,14 @@
       <c r="C70" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>201</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -1567,8 +2365,14 @@
       <c r="C71" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -1578,8 +2382,14 @@
       <c r="C72" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -1589,8 +2399,14 @@
       <c r="C73" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>204</v>
+      </c>
+      <c r="E73" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -1600,8 +2416,14 @@
       <c r="C74" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>205</v>
+      </c>
+      <c r="E74" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -1611,8 +2433,14 @@
       <c r="C75" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>206</v>
+      </c>
+      <c r="E75" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -1622,8 +2450,14 @@
       <c r="C76" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -1633,8 +2467,14 @@
       <c r="C77" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>208</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -1644,8 +2484,14 @@
       <c r="C78" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -1655,8 +2501,14 @@
       <c r="C79" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -1666,8 +2518,14 @@
       <c r="C80" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" t="s">
+        <v>211</v>
+      </c>
+      <c r="E80" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -1677,8 +2535,14 @@
       <c r="C81" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" t="s">
+        <v>212</v>
+      </c>
+      <c r="E81" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -1688,8 +2552,14 @@
       <c r="C82" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" t="s">
+        <v>213</v>
+      </c>
+      <c r="E82" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -1699,8 +2569,14 @@
       <c r="C83" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" t="s">
+        <v>214</v>
+      </c>
+      <c r="E83" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -1710,8 +2586,14 @@
       <c r="C84" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" t="s">
+        <v>215</v>
+      </c>
+      <c r="E84" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -1721,8 +2603,14 @@
       <c r="C85" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" t="s">
+        <v>216</v>
+      </c>
+      <c r="E85" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -1732,8 +2620,14 @@
       <c r="C86" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" t="s">
+        <v>217</v>
+      </c>
+      <c r="E86" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -1743,8 +2637,14 @@
       <c r="C87" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>218</v>
+      </c>
+      <c r="E87" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -1754,8 +2654,14 @@
       <c r="C88" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" t="s">
+        <v>219</v>
+      </c>
+      <c r="E88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -1765,8 +2671,14 @@
       <c r="C89" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" t="s">
+        <v>220</v>
+      </c>
+      <c r="E89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -1776,8 +2688,14 @@
       <c r="C90" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" t="s">
+        <v>221</v>
+      </c>
+      <c r="E90" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -1787,8 +2705,14 @@
       <c r="C91" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" t="s">
+        <v>222</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -1798,8 +2722,14 @@
       <c r="C92" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" t="s">
+        <v>223</v>
+      </c>
+      <c r="E92" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -1809,8 +2739,14 @@
       <c r="C93" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -1820,8 +2756,14 @@
       <c r="C94" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" t="s">
+        <v>225</v>
+      </c>
+      <c r="E94" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -1831,8 +2773,14 @@
       <c r="C95" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>226</v>
+      </c>
+      <c r="E95" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -1842,8 +2790,14 @@
       <c r="C96" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" t="s">
+        <v>227</v>
+      </c>
+      <c r="E96" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -1853,8 +2807,14 @@
       <c r="C97" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" t="s">
+        <v>228</v>
+      </c>
+      <c r="E97" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -1864,8 +2824,14 @@
       <c r="C98" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -1875,8 +2841,14 @@
       <c r="C99" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" t="s">
+        <v>230</v>
+      </c>
+      <c r="E99" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -1886,8 +2858,14 @@
       <c r="C100" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -1897,8 +2875,14 @@
       <c r="C101" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" t="s">
+        <v>232</v>
+      </c>
+      <c r="E101" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -1908,8 +2892,14 @@
       <c r="C102" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" t="s">
+        <v>233</v>
+      </c>
+      <c r="E102" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -1919,8 +2909,14 @@
       <c r="C103" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>234</v>
+      </c>
+      <c r="E103" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -1930,8 +2926,14 @@
       <c r="C104" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" t="s">
+        <v>235</v>
+      </c>
+      <c r="E104" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -1941,8 +2943,14 @@
       <c r="C105" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" t="s">
+        <v>236</v>
+      </c>
+      <c r="E105" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -1952,8 +2960,14 @@
       <c r="C106" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" t="s">
+        <v>237</v>
+      </c>
+      <c r="E106" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -1963,8 +2977,14 @@
       <c r="C107" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" t="s">
+        <v>238</v>
+      </c>
+      <c r="E107" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -1974,8 +2994,14 @@
       <c r="C108" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" t="s">
+        <v>239</v>
+      </c>
+      <c r="E108" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -1985,8 +3011,14 @@
       <c r="C109" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" t="s">
+        <v>240</v>
+      </c>
+      <c r="E109" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -1996,8 +3028,14 @@
       <c r="C110" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" t="s">
+        <v>241</v>
+      </c>
+      <c r="E110" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2007,8 +3045,14 @@
       <c r="C111" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" t="s">
+        <v>242</v>
+      </c>
+      <c r="E111" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -2018,8 +3062,14 @@
       <c r="C112" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" t="s">
+        <v>243</v>
+      </c>
+      <c r="E112" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2029,8 +3079,14 @@
       <c r="C113" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" t="s">
+        <v>244</v>
+      </c>
+      <c r="E113" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2040,8 +3096,14 @@
       <c r="C114" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" t="s">
+        <v>245</v>
+      </c>
+      <c r="E114" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2051,8 +3113,14 @@
       <c r="C115" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" t="s">
+        <v>246</v>
+      </c>
+      <c r="E115" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2062,8 +3130,14 @@
       <c r="C116" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" t="s">
+        <v>247</v>
+      </c>
+      <c r="E116" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2073,8 +3147,14 @@
       <c r="C117" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" t="s">
+        <v>248</v>
+      </c>
+      <c r="E117" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2084,8 +3164,14 @@
       <c r="C118" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" t="s">
+        <v>249</v>
+      </c>
+      <c r="E118" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2095,8 +3181,14 @@
       <c r="C119" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" t="s">
+        <v>250</v>
+      </c>
+      <c r="E119" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2106,8 +3198,14 @@
       <c r="C120" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" t="s">
+        <v>251</v>
+      </c>
+      <c r="E120" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2117,8 +3215,14 @@
       <c r="C121" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" t="s">
+        <v>252</v>
+      </c>
+      <c r="E121" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2128,8 +3232,14 @@
       <c r="C122" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" t="s">
+        <v>253</v>
+      </c>
+      <c r="E122" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -2139,8 +3249,14 @@
       <c r="C123" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" t="s">
+        <v>254</v>
+      </c>
+      <c r="E123" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -2150,8 +3266,14 @@
       <c r="C124" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" t="s">
+        <v>255</v>
+      </c>
+      <c r="E124" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -2161,8 +3283,14 @@
       <c r="C125" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" t="s">
+        <v>256</v>
+      </c>
+      <c r="E125" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -2172,8 +3300,14 @@
       <c r="C126" s="1" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" t="s">
+        <v>257</v>
+      </c>
+      <c r="E126" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -2182,6 +3316,12 @@
       </c>
       <c r="C127" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="D127" t="s">
+        <v>258</v>
+      </c>
+      <c r="E127" s="1">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
